--- a/rtos-api-analysis/results/freertos-10.5.1_runtime_info.xlsx
+++ b/rtos-api-analysis/results/freertos-10.5.1_runtime_info.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H107"/>
+  <dimension ref="A1:I107"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -466,6 +466,11 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
+          <t>StoppedByMaxTime</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
           <t>Last Instruction</t>
         </is>
       </c>
@@ -477,7 +482,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>33</v>
+        <v>6</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -505,6 +510,11 @@
         </is>
       </c>
       <c r="H2" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
         <is>
           <t>NA</t>
         </is>
@@ -517,7 +527,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -545,6 +555,11 @@
         </is>
       </c>
       <c r="H3" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
         <is>
           <t>NA</t>
         </is>
@@ -557,7 +572,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -585,6 +600,11 @@
         </is>
       </c>
       <c r="H4" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
         <is>
           <t>NA</t>
         </is>
@@ -597,7 +617,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -625,6 +645,11 @@
         </is>
       </c>
       <c r="H5" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
         <is>
           <t>NA</t>
         </is>
@@ -637,7 +662,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -665,6 +690,11 @@
         </is>
       </c>
       <c r="H6" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
         <is>
           <t>NA</t>
         </is>
@@ -704,6 +734,11 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
           <t xml:space="preserve">KLEE: Execute: test-rtos/freertos-10.5.1/Source/tasks.c:2203
 </t>
         </is>
@@ -716,7 +751,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -744,6 +779,11 @@
         </is>
       </c>
       <c r="H8" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
         <is>
           <t>NA</t>
         </is>
@@ -785,6 +825,11 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
           <t>NA</t>
         </is>
       </c>
@@ -796,7 +841,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -824,6 +869,11 @@
         </is>
       </c>
       <c r="H10" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
         <is>
           <t>NA</t>
         </is>
@@ -836,7 +886,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>346</v>
+        <v>84</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -864,6 +914,11 @@
         </is>
       </c>
       <c r="H11" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
         <is>
           <t>NA</t>
         </is>
@@ -905,6 +960,11 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
           <t>NA</t>
         </is>
       </c>
@@ -945,6 +1005,11 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
           <t>NA</t>
         </is>
       </c>
@@ -955,37 +1020,41 @@
           <t>test_MPU_xTaskIncrementTick</t>
         </is>
       </c>
-      <c r="B14" t="n">
-        <v>5</v>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>2332</t>
-        </is>
-      </c>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">KLEE: Execute: test-rtos/freertos-10.5.1/Source/tasks.c:2797
+</t>
         </is>
       </c>
     </row>
@@ -996,7 +1065,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>33</v>
+        <v>6</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -1024,6 +1093,11 @@
         </is>
       </c>
       <c r="H15" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
         <is>
           <t>NA</t>
         </is>
@@ -1036,7 +1110,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -1064,6 +1138,11 @@
         </is>
       </c>
       <c r="H16" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
         <is>
           <t>NA</t>
         </is>
@@ -1105,6 +1184,11 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
           <t>NA</t>
         </is>
       </c>
@@ -1116,7 +1200,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -1144,6 +1228,11 @@
         </is>
       </c>
       <c r="H18" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
         <is>
           <t>NA</t>
         </is>
@@ -1156,7 +1245,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -1184,6 +1273,11 @@
         </is>
       </c>
       <c r="H19" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
         <is>
           <t>NA</t>
         </is>
@@ -1225,6 +1319,11 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
           <t>NA</t>
         </is>
       </c>
@@ -1236,7 +1335,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -1264,6 +1363,11 @@
         </is>
       </c>
       <c r="H21" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
         <is>
           <t>NA</t>
         </is>
@@ -1275,37 +1379,41 @@
           <t>test_MPU_xStreamBufferReceive</t>
         </is>
       </c>
-      <c r="B22" t="n">
-        <v>9450</v>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>12240</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>1003950</t>
-        </is>
-      </c>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr"/>
       <c r="E22" t="inlineStr">
         <is>
-          <t>12240</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">KLEE: Execute: test-rtos/freertos-10.5.1/Source/stream_buffer.c:1329
+</t>
         </is>
       </c>
     </row>
@@ -1345,6 +1453,11 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
           <t>NA</t>
         </is>
       </c>
@@ -1356,7 +1469,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -1384,6 +1497,11 @@
         </is>
       </c>
       <c r="H24" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
         <is>
           <t>NA</t>
         </is>
@@ -1396,7 +1514,7 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -1424,6 +1542,11 @@
         </is>
       </c>
       <c r="H25" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
         <is>
           <t>NA</t>
         </is>
@@ -1436,7 +1559,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -1464,6 +1587,11 @@
         </is>
       </c>
       <c r="H26" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
         <is>
           <t>NA</t>
         </is>
@@ -1505,6 +1633,11 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
           <t>NA</t>
         </is>
       </c>
@@ -1516,7 +1649,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -1544,6 +1677,11 @@
         </is>
       </c>
       <c r="H28" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
         <is>
           <t>NA</t>
         </is>
@@ -1556,7 +1694,7 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -1584,6 +1722,11 @@
         </is>
       </c>
       <c r="H29" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
         <is>
           <t>NA</t>
         </is>
@@ -1596,7 +1739,7 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -1624,6 +1767,11 @@
         </is>
       </c>
       <c r="H30" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
         <is>
           <t>NA</t>
         </is>
@@ -1636,7 +1784,7 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -1664,6 +1812,11 @@
         </is>
       </c>
       <c r="H31" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
         <is>
           <t>NA</t>
         </is>
@@ -1705,6 +1858,11 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
           <t>NA</t>
         </is>
       </c>
@@ -1716,7 +1874,7 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -1744,6 +1902,11 @@
         </is>
       </c>
       <c r="H33" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
         <is>
           <t>NA</t>
         </is>
@@ -1756,7 +1919,7 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -1784,6 +1947,11 @@
         </is>
       </c>
       <c r="H34" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
         <is>
           <t>NA</t>
         </is>
@@ -1796,7 +1964,7 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -1824,6 +1992,11 @@
         </is>
       </c>
       <c r="H35" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
         <is>
           <t>NA</t>
         </is>
@@ -1836,7 +2009,7 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -1864,6 +2037,11 @@
         </is>
       </c>
       <c r="H36" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
         <is>
           <t>NA</t>
         </is>
@@ -1876,7 +2054,7 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -1904,6 +2082,11 @@
         </is>
       </c>
       <c r="H37" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
         <is>
           <t>NA</t>
         </is>
@@ -1916,7 +2099,7 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -1944,6 +2127,11 @@
         </is>
       </c>
       <c r="H38" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
         <is>
           <t>NA</t>
         </is>
@@ -1956,7 +2144,7 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -1965,25 +2153,30 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>5371</t>
+          <t>6119</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>86</t>
+          <t>158</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>20</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
         <is>
           <t>NA</t>
         </is>
@@ -1996,7 +2189,7 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -2024,6 +2217,11 @@
         </is>
       </c>
       <c r="H40" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
         <is>
           <t>NA</t>
         </is>
@@ -2063,7 +2261,12 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t xml:space="preserve">KLEE: Execute: test-rtos/freertos-10.5.1/Source/tasks.c:2282
+          <t>no</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">KLEE: Execute: test-rtos/freertos-10.5.1/Source/tasks.c:3189
 </t>
         </is>
       </c>
@@ -2075,7 +2278,7 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -2103,6 +2306,11 @@
         </is>
       </c>
       <c r="H42" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
         <is>
           <t>NA</t>
         </is>
@@ -2115,7 +2323,7 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -2143,6 +2351,11 @@
         </is>
       </c>
       <c r="H43" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
         <is>
           <t>NA</t>
         </is>
@@ -2155,7 +2368,7 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -2183,6 +2396,11 @@
         </is>
       </c>
       <c r="H44" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
         <is>
           <t>NA</t>
         </is>
@@ -2195,34 +2413,39 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>133</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>3615</t>
+          <t>7841</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>133</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>17</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
         <is>
           <t>NA</t>
         </is>
@@ -2235,7 +2458,7 @@
         </is>
       </c>
       <c r="B46" t="n">
-        <v>6118</v>
+        <v>6619</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -2263,6 +2486,11 @@
         </is>
       </c>
       <c r="H46" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
         <is>
           <t>NA</t>
         </is>
@@ -2275,7 +2503,7 @@
         </is>
       </c>
       <c r="B47" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -2303,6 +2531,11 @@
         </is>
       </c>
       <c r="H47" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
         <is>
           <t>NA</t>
         </is>
@@ -2344,6 +2577,11 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
           <t>NA</t>
         </is>
       </c>
@@ -2355,7 +2593,7 @@
         </is>
       </c>
       <c r="B49" t="n">
-        <v>45</v>
+        <v>12</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -2383,6 +2621,11 @@
         </is>
       </c>
       <c r="H49" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
         <is>
           <t>NA</t>
         </is>
@@ -2395,7 +2638,7 @@
         </is>
       </c>
       <c r="B50" t="n">
-        <v>221</v>
+        <v>43</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -2423,6 +2666,11 @@
         </is>
       </c>
       <c r="H50" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
         <is>
           <t>NA</t>
         </is>
@@ -2435,7 +2683,7 @@
         </is>
       </c>
       <c r="B51" t="n">
-        <v>36</v>
+        <v>6</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -2463,6 +2711,11 @@
         </is>
       </c>
       <c r="H51" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
         <is>
           <t>NA</t>
         </is>
@@ -2475,7 +2728,7 @@
         </is>
       </c>
       <c r="B52" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -2484,25 +2737,30 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>1164</t>
+          <t>1234</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>22</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>6</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
         <is>
           <t>NA</t>
         </is>
@@ -2542,6 +2800,11 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
           <t xml:space="preserve">KLEE: Execute: test-rtos/freertos-10.5.1/Source/tasks.c:4824
 </t>
         </is>
@@ -2581,1926 +2844,2170 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t xml:space="preserve">KLEE: Execute: test-rtos/freertos-10.5.1/Source/tasks.c:2203
+</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>test_MPU_vTaskStartScheduler</t>
+        </is>
+      </c>
+      <c r="B55" t="n">
+        <v>1</v>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>4398</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>test_MPU_uxTaskGetSystemState</t>
+        </is>
+      </c>
+      <c r="B56" t="n">
+        <v>5</v>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>111</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>15396</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>111</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>test_MPU_xTimerGenericCommand</t>
+        </is>
+      </c>
+      <c r="B57" t="n">
+        <v>4317</v>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>90832</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>4381845</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>90832</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>test_MPU_xQueueGetMutexHolder</t>
+        </is>
+      </c>
+      <c r="B58" t="n">
+        <v>0</v>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>815</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>test_MPU_eTaskGetState</t>
+        </is>
+      </c>
+      <c r="B59" t="n">
+        <v>1</v>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>1425</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>test_MPU_xStreamBufferSpacesAvailable</t>
+        </is>
+      </c>
+      <c r="B60" t="n">
+        <v>1</v>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>955</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>test_MPU_vTaskSuspendAll</t>
+        </is>
+      </c>
+      <c r="B61" t="n">
+        <v>0</v>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>588</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>test_MPU_xStreamBufferGenericCreateStatic</t>
+        </is>
+      </c>
+      <c r="B62" t="n">
+        <v>3</v>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>260</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>15656</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>260</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>test_MPU_xEventGroupCreate</t>
+        </is>
+      </c>
+      <c r="B63" t="n">
+        <v>0</v>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>869</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>test_MPU_xEventGroupSetBits</t>
+        </is>
+      </c>
+      <c r="B64" t="n">
+        <v>21</v>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>720</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>48918</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>720</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>test_MPU_xStreamBufferIsEmpty</t>
+        </is>
+      </c>
+      <c r="B65" t="n">
+        <v>1</v>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>805</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>test_MPU_xTaskResumeAll</t>
+        </is>
+      </c>
+      <c r="B66" t="n">
+        <v>0</v>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>714</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>test_MPU_vTimerSetReloadMode</t>
+        </is>
+      </c>
+      <c r="B67" t="n">
+        <v>0</v>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>860</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>test_MPU_xTimerPendFunctionCall</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr"/>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t xml:space="preserve">KLEE: Execute: test-rtos/freertos-10.5.1/Source/tasks.c:2203
+</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>test_MPU_xTimerGetTimerDaemonTaskHandle</t>
+        </is>
+      </c>
+      <c r="B69" t="n">
+        <v>0</v>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>624</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>test_MPU_xQueueGenericReset</t>
+        </is>
+      </c>
+      <c r="B70" t="n">
+        <v>9</v>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>3906</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>test_MPU_xQueueCreateMutexStatic</t>
+        </is>
+      </c>
+      <c r="B71" t="n">
+        <v>228</v>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>6556</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>347364</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>6556</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>test_MPU_xTaskCallApplicationTaskHook</t>
+        </is>
+      </c>
+      <c r="B72" t="n">
+        <v>0</v>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>876</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>test_MPU_uxTaskGetStackHighWaterMark</t>
+        </is>
+      </c>
+      <c r="B73" t="n">
+        <v>0</v>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>1254</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>test_MPU_ucQueueGetQueueType</t>
+        </is>
+      </c>
+      <c r="B74" t="n">
+        <v>0</v>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>640</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>test_MPU_xQueueCreateMutex</t>
+        </is>
+      </c>
+      <c r="B75" t="n">
+        <v>149</v>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>4319</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>231087</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>4319</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>test_MPU_ulTaskGetIdleRunTimeCounter</t>
+        </is>
+      </c>
+      <c r="B76" t="n">
+        <v>0</v>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>609</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>test_MPU_xQueueCreateSet</t>
+        </is>
+      </c>
+      <c r="B77" t="n">
+        <v>1</v>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>2275</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>test_MPU_xQueueGiveMutexRecursive</t>
+        </is>
+      </c>
+      <c r="B78" t="n">
+        <v>291</v>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>8064</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>433444</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>8064</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>test_MPU_xTimerGetExpiryTime</t>
+        </is>
+      </c>
+      <c r="B79" t="n">
+        <v>0</v>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>735</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>test_MPU_xEventGroupClearBits</t>
+        </is>
+      </c>
+      <c r="B80" t="n">
+        <v>0</v>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>996</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>test_MPU_vStreamBufferDelete</t>
+        </is>
+      </c>
+      <c r="B81" t="n">
+        <v>0</v>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>889</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>test_MPU_vQueueAddToRegistry</t>
+        </is>
+      </c>
+      <c r="B82" t="n">
+        <v>0</v>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>1393</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>test_MPU_xStreamBufferGenericCreate</t>
+        </is>
+      </c>
+      <c r="B83" t="n">
+        <v>2</v>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>140</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>9706</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>140</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>test_MPU_vQueueUnregisterQueue</t>
+        </is>
+      </c>
+      <c r="B84" t="n">
+        <v>0</v>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>1024</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>test_MPU_xTaskGetCurrentTaskHandle</t>
+        </is>
+      </c>
+      <c r="B85" t="n">
+        <v>0</v>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>619</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>test_MPU_xTaskGetIdleTaskHandle</t>
+        </is>
+      </c>
+      <c r="B86" t="n">
+        <v>0</v>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>624</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>test_MPU_ulTaskGenericNotifyValueClear</t>
+        </is>
+      </c>
+      <c r="B87" t="n">
+        <v>1</v>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>972</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>test_MPU_uxQueueSpacesAvailable</t>
+        </is>
+      </c>
+      <c r="B88" t="n">
+        <v>0</v>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>760</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>test_MPU_xTaskGenericNotifyStateClear</t>
+        </is>
+      </c>
+      <c r="B89" t="n">
+        <v>2</v>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>1376</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>test_MPU_xStreamBufferReset</t>
+        </is>
+      </c>
+      <c r="B90" t="n">
+        <v>1</v>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>1865</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>test_MPU_xEventGroupSync</t>
+        </is>
+      </c>
+      <c r="B91" t="n">
+        <v>749</v>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>26070</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>2484512</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>26070</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>test_MPU_xTaskCatchUpTicks</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr"/>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t xml:space="preserve">KLEE: Execute: test-rtos/freertos-10.5.1/Source/tasks.c:2793
+</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>test_MPU_xTaskGetApplicationTaskTag</t>
+        </is>
+      </c>
+      <c r="B93" t="n">
+        <v>1</v>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>790</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>test_MPU_xQueueGenericSend</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr"/>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
           <t xml:space="preserve">KLEE: Execute: test-rtos/freertos-10.5.1/Source/tasks.c:2201
 </t>
         </is>
       </c>
     </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>test_MPU_vTaskStartScheduler</t>
-        </is>
-      </c>
-      <c r="B55" t="n">
-        <v>4</v>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="D55" t="inlineStr">
-        <is>
-          <t>4398</t>
-        </is>
-      </c>
-      <c r="E55" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="F55" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G55" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="H55" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>test_MPU_uxTaskGetSystemState</t>
-        </is>
-      </c>
-      <c r="B56" t="n">
-        <v>4</v>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>99</t>
-        </is>
-      </c>
-      <c r="D56" t="inlineStr">
-        <is>
-          <t>10609</t>
-        </is>
-      </c>
-      <c r="E56" t="inlineStr">
-        <is>
-          <t>44</t>
-        </is>
-      </c>
-      <c r="F56" t="inlineStr">
-        <is>
-          <t>55</t>
-        </is>
-      </c>
-      <c r="G56" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="H56" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>test_MPU_xTimerGenericCommand</t>
-        </is>
-      </c>
-      <c r="B57" t="n">
-        <v>22383</v>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>90832</t>
-        </is>
-      </c>
-      <c r="D57" t="inlineStr">
-        <is>
-          <t>4381845</t>
-        </is>
-      </c>
-      <c r="E57" t="inlineStr">
-        <is>
-          <t>90832</t>
-        </is>
-      </c>
-      <c r="F57" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G57" t="inlineStr">
-        <is>
-          <t>44</t>
-        </is>
-      </c>
-      <c r="H57" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>test_MPU_xQueueGetMutexHolder</t>
-        </is>
-      </c>
-      <c r="B58" t="n">
-        <v>1</v>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="D58" t="inlineStr">
-        <is>
-          <t>815</t>
-        </is>
-      </c>
-      <c r="E58" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="F58" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G58" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="H58" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>test_MPU_eTaskGetState</t>
-        </is>
-      </c>
-      <c r="B59" t="n">
-        <v>2</v>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="D59" t="inlineStr">
-        <is>
-          <t>1425</t>
-        </is>
-      </c>
-      <c r="E59" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="F59" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G59" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="H59" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t>test_MPU_xStreamBufferSpacesAvailable</t>
-        </is>
-      </c>
-      <c r="B60" t="n">
-        <v>1</v>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="D60" t="inlineStr">
-        <is>
-          <t>955</t>
-        </is>
-      </c>
-      <c r="E60" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="F60" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G60" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="H60" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>test_MPU_vTaskSuspendAll</t>
-        </is>
-      </c>
-      <c r="B61" t="n">
-        <v>1</v>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="D61" t="inlineStr">
-        <is>
-          <t>588</t>
-        </is>
-      </c>
-      <c r="E61" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="F61" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G61" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="H61" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>test_MPU_xStreamBufferGenericCreateStatic</t>
-        </is>
-      </c>
-      <c r="B62" t="n">
-        <v>15</v>
-      </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>260</t>
-        </is>
-      </c>
-      <c r="D62" t="inlineStr">
-        <is>
-          <t>15656</t>
-        </is>
-      </c>
-      <c r="E62" t="inlineStr">
-        <is>
-          <t>260</t>
-        </is>
-      </c>
-      <c r="F62" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G62" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="H62" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>test_MPU_xEventGroupCreate</t>
-        </is>
-      </c>
-      <c r="B63" t="n">
-        <v>1</v>
-      </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="D63" t="inlineStr">
-        <is>
-          <t>869</t>
-        </is>
-      </c>
-      <c r="E63" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="F63" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G63" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="H63" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>test_MPU_xEventGroupSetBits</t>
-        </is>
-      </c>
-      <c r="B64" t="n">
-        <v>93</v>
-      </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>720</t>
-        </is>
-      </c>
-      <c r="D64" t="inlineStr">
-        <is>
-          <t>48918</t>
-        </is>
-      </c>
-      <c r="E64" t="inlineStr">
-        <is>
-          <t>720</t>
-        </is>
-      </c>
-      <c r="F64" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G64" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="H64" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="inlineStr">
-        <is>
-          <t>test_MPU_xStreamBufferIsEmpty</t>
-        </is>
-      </c>
-      <c r="B65" t="n">
-        <v>2</v>
-      </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="D65" t="inlineStr">
-        <is>
-          <t>805</t>
-        </is>
-      </c>
-      <c r="E65" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="F65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G65" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="H65" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="inlineStr">
-        <is>
-          <t>test_MPU_xTaskResumeAll</t>
-        </is>
-      </c>
-      <c r="B66" t="n">
-        <v>1</v>
-      </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="D66" t="inlineStr">
-        <is>
-          <t>714</t>
-        </is>
-      </c>
-      <c r="E66" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="F66" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G66" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="H66" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="inlineStr">
-        <is>
-          <t>test_MPU_vTimerSetReloadMode</t>
-        </is>
-      </c>
-      <c r="B67" t="n">
-        <v>2</v>
-      </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="D67" t="inlineStr">
-        <is>
-          <t>860</t>
-        </is>
-      </c>
-      <c r="E67" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="F67" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G67" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="H67" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="inlineStr">
-        <is>
-          <t>test_MPU_xTimerPendFunctionCall</t>
-        </is>
-      </c>
-      <c r="B68" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="C68" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="D68" t="inlineStr"/>
-      <c r="E68" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="F68" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="G68" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="H68" t="inlineStr">
-        <is>
-          <t xml:space="preserve">KLEE: Execute: test-rtos/freertos-10.5.1/Source/tasks.c:2203
-</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="inlineStr">
-        <is>
-          <t>test_MPU_xTimerGetTimerDaemonTaskHandle</t>
-        </is>
-      </c>
-      <c r="B69" t="n">
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>test_MPU_pcQueueGetName</t>
+        </is>
+      </c>
+      <c r="B95" t="n">
         <v>0</v>
       </c>
-      <c r="C69" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="D69" t="inlineStr">
-        <is>
-          <t>624</t>
-        </is>
-      </c>
-      <c r="E69" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="F69" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G69" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="H69" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="inlineStr">
-        <is>
-          <t>test_MPU_xQueueGenericReset</t>
-        </is>
-      </c>
-      <c r="B70" t="n">
-        <v>17</v>
-      </c>
-      <c r="C70" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
-      <c r="D70" t="inlineStr">
-        <is>
-          <t>3906</t>
-        </is>
-      </c>
-      <c r="E70" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
-      <c r="F70" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G70" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="H70" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="inlineStr">
-        <is>
-          <t>test_MPU_xQueueCreateMutexStatic</t>
-        </is>
-      </c>
-      <c r="B71" t="n">
-        <v>1406</v>
-      </c>
-      <c r="C71" t="inlineStr">
-        <is>
-          <t>6556</t>
-        </is>
-      </c>
-      <c r="D71" t="inlineStr">
-        <is>
-          <t>347364</t>
-        </is>
-      </c>
-      <c r="E71" t="inlineStr">
-        <is>
-          <t>6556</t>
-        </is>
-      </c>
-      <c r="F71" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G71" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="H71" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="inlineStr">
-        <is>
-          <t>test_MPU_xTaskCallApplicationTaskHook</t>
-        </is>
-      </c>
-      <c r="B72" t="n">
-        <v>1</v>
-      </c>
-      <c r="C72" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="D72" t="inlineStr">
-        <is>
-          <t>876</t>
-        </is>
-      </c>
-      <c r="E72" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="F72" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G72" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="H72" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="inlineStr">
-        <is>
-          <t>test_MPU_uxTaskGetStackHighWaterMark</t>
-        </is>
-      </c>
-      <c r="B73" t="n">
-        <v>2</v>
-      </c>
-      <c r="C73" t="inlineStr">
+      <c r="C95" t="inlineStr">
         <is>
           <t>22</t>
         </is>
       </c>
-      <c r="D73" t="inlineStr">
-        <is>
-          <t>1177</t>
-        </is>
-      </c>
-      <c r="E73" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="F73" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="G73" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="H73" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="inlineStr">
-        <is>
-          <t>test_MPU_ucQueueGetQueueType</t>
-        </is>
-      </c>
-      <c r="B74" t="n">
-        <v>1</v>
-      </c>
-      <c r="C74" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="D74" t="inlineStr">
-        <is>
-          <t>640</t>
-        </is>
-      </c>
-      <c r="E74" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="F74" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G74" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="H74" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="inlineStr">
-        <is>
-          <t>test_MPU_xQueueCreateMutex</t>
-        </is>
-      </c>
-      <c r="B75" t="n">
-        <v>737</v>
-      </c>
-      <c r="C75" t="inlineStr">
-        <is>
-          <t>4319</t>
-        </is>
-      </c>
-      <c r="D75" t="inlineStr">
-        <is>
-          <t>231087</t>
-        </is>
-      </c>
-      <c r="E75" t="inlineStr">
-        <is>
-          <t>4319</t>
-        </is>
-      </c>
-      <c r="F75" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G75" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="H75" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" t="inlineStr">
-        <is>
-          <t>test_MPU_ulTaskGetIdleRunTimeCounter</t>
-        </is>
-      </c>
-      <c r="B76" t="n">
-        <v>1</v>
-      </c>
-      <c r="C76" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="D76" t="inlineStr">
-        <is>
-          <t>609</t>
-        </is>
-      </c>
-      <c r="E76" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="F76" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G76" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="H76" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" t="inlineStr">
-        <is>
-          <t>test_MPU_xQueueCreateSet</t>
-        </is>
-      </c>
-      <c r="B77" t="n">
-        <v>3</v>
-      </c>
-      <c r="C77" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="D77" t="inlineStr">
-        <is>
-          <t>2275</t>
-        </is>
-      </c>
-      <c r="E77" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="F77" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G77" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="H77" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" t="inlineStr">
-        <is>
-          <t>test_MPU_xQueueGiveMutexRecursive</t>
-        </is>
-      </c>
-      <c r="B78" t="n">
-        <v>1859</v>
-      </c>
-      <c r="C78" t="inlineStr">
-        <is>
-          <t>8064</t>
-        </is>
-      </c>
-      <c r="D78" t="inlineStr">
-        <is>
-          <t>433444</t>
-        </is>
-      </c>
-      <c r="E78" t="inlineStr">
-        <is>
-          <t>8064</t>
-        </is>
-      </c>
-      <c r="F78" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G78" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
-      <c r="H78" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" t="inlineStr">
-        <is>
-          <t>test_MPU_xTimerGetExpiryTime</t>
-        </is>
-      </c>
-      <c r="B79" t="n">
-        <v>2</v>
-      </c>
-      <c r="C79" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="D79" t="inlineStr">
-        <is>
-          <t>735</t>
-        </is>
-      </c>
-      <c r="E79" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="F79" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G79" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="H79" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" t="inlineStr">
-        <is>
-          <t>test_MPU_xEventGroupClearBits</t>
-        </is>
-      </c>
-      <c r="B80" t="n">
-        <v>1</v>
-      </c>
-      <c r="C80" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="D80" t="inlineStr">
-        <is>
-          <t>996</t>
-        </is>
-      </c>
-      <c r="E80" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="F80" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G80" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="H80" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" t="inlineStr">
-        <is>
-          <t>test_MPU_vStreamBufferDelete</t>
-        </is>
-      </c>
-      <c r="B81" t="n">
-        <v>1</v>
-      </c>
-      <c r="C81" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="D81" t="inlineStr">
-        <is>
-          <t>889</t>
-        </is>
-      </c>
-      <c r="E81" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="F81" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G81" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="H81" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" t="inlineStr">
-        <is>
-          <t>test_MPU_vQueueAddToRegistry</t>
-        </is>
-      </c>
-      <c r="B82" t="n">
-        <v>2</v>
-      </c>
-      <c r="C82" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
-      <c r="D82" t="inlineStr">
-        <is>
-          <t>1393</t>
-        </is>
-      </c>
-      <c r="E82" t="inlineStr">
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>1043</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
         <is>
           <t>22</t>
         </is>
       </c>
-      <c r="F82" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="G82" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="H82" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" t="inlineStr">
-        <is>
-          <t>test_MPU_xStreamBufferGenericCreate</t>
-        </is>
-      </c>
-      <c r="B83" t="n">
-        <v>3</v>
-      </c>
-      <c r="C83" t="inlineStr">
-        <is>
-          <t>140</t>
-        </is>
-      </c>
-      <c r="D83" t="inlineStr">
-        <is>
-          <t>9706</t>
-        </is>
-      </c>
-      <c r="E83" t="inlineStr">
-        <is>
-          <t>140</t>
-        </is>
-      </c>
-      <c r="F83" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G83" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="H83" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" t="inlineStr">
-        <is>
-          <t>test_MPU_vQueueUnregisterQueue</t>
-        </is>
-      </c>
-      <c r="B84" t="n">
-        <v>1</v>
-      </c>
-      <c r="C84" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="D84" t="inlineStr">
-        <is>
-          <t>1024</t>
-        </is>
-      </c>
-      <c r="E84" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="F84" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="G84" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="H84" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" t="inlineStr">
-        <is>
-          <t>test_MPU_xTaskGetCurrentTaskHandle</t>
-        </is>
-      </c>
-      <c r="B85" t="n">
-        <v>1</v>
-      </c>
-      <c r="C85" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="D85" t="inlineStr">
-        <is>
-          <t>619</t>
-        </is>
-      </c>
-      <c r="E85" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="F85" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G85" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="H85" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" t="inlineStr">
-        <is>
-          <t>test_MPU_xTaskGetIdleTaskHandle</t>
-        </is>
-      </c>
-      <c r="B86" t="n">
-        <v>1</v>
-      </c>
-      <c r="C86" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="D86" t="inlineStr">
-        <is>
-          <t>624</t>
-        </is>
-      </c>
-      <c r="E86" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="F86" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G86" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="H86" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" t="inlineStr">
-        <is>
-          <t>test_MPU_ulTaskGenericNotifyValueClear</t>
-        </is>
-      </c>
-      <c r="B87" t="n">
-        <v>1</v>
-      </c>
-      <c r="C87" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="D87" t="inlineStr">
-        <is>
-          <t>972</t>
-        </is>
-      </c>
-      <c r="E87" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="F87" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G87" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="H87" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" t="inlineStr">
-        <is>
-          <t>test_MPU_uxQueueSpacesAvailable</t>
-        </is>
-      </c>
-      <c r="B88" t="n">
-        <v>1</v>
-      </c>
-      <c r="C88" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="D88" t="inlineStr">
-        <is>
-          <t>760</t>
-        </is>
-      </c>
-      <c r="E88" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="F88" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G88" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="H88" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" t="inlineStr">
-        <is>
-          <t>test_MPU_xTaskGenericNotifyStateClear</t>
-        </is>
-      </c>
-      <c r="B89" t="n">
-        <v>7</v>
-      </c>
-      <c r="C89" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="D89" t="inlineStr">
-        <is>
-          <t>1376</t>
-        </is>
-      </c>
-      <c r="E89" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="F89" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G89" t="inlineStr">
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="H89" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" t="inlineStr">
-        <is>
-          <t>test_MPU_xStreamBufferReset</t>
-        </is>
-      </c>
-      <c r="B90" t="n">
-        <v>2</v>
-      </c>
-      <c r="C90" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="D90" t="inlineStr">
-        <is>
-          <t>1865</t>
-        </is>
-      </c>
-      <c r="E90" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="F90" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G90" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="H90" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" t="inlineStr">
-        <is>
-          <t>test_MPU_xEventGroupSync</t>
-        </is>
-      </c>
-      <c r="B91" t="n">
-        <v>3418</v>
-      </c>
-      <c r="C91" t="inlineStr">
-        <is>
-          <t>26070</t>
-        </is>
-      </c>
-      <c r="D91" t="inlineStr">
-        <is>
-          <t>2484512</t>
-        </is>
-      </c>
-      <c r="E91" t="inlineStr">
-        <is>
-          <t>26070</t>
-        </is>
-      </c>
-      <c r="F91" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G91" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="H91" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" t="inlineStr">
-        <is>
-          <t>test_MPU_xTaskCatchUpTicks</t>
-        </is>
-      </c>
-      <c r="B92" t="n">
-        <v>3</v>
-      </c>
-      <c r="C92" t="inlineStr">
-        <is>
-          <t>58</t>
-        </is>
-      </c>
-      <c r="D92" t="inlineStr">
-        <is>
-          <t>3821</t>
-        </is>
-      </c>
-      <c r="E92" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="F92" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
-      </c>
-      <c r="G92" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="H92" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" t="inlineStr">
-        <is>
-          <t>test_MPU_xTaskGetApplicationTaskTag</t>
-        </is>
-      </c>
-      <c r="B93" t="n">
-        <v>0</v>
-      </c>
-      <c r="C93" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="D93" t="inlineStr">
-        <is>
-          <t>790</t>
-        </is>
-      </c>
-      <c r="E93" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="F93" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G93" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="H93" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" t="inlineStr">
-        <is>
-          <t>test_MPU_xQueueGenericSend</t>
-        </is>
-      </c>
-      <c r="B94" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="C94" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="D94" t="inlineStr"/>
-      <c r="E94" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="F94" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="G94" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="H94" t="inlineStr">
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>test_MPU_xQueueSemaphoreTake</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr"/>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr">
         <is>
           <t xml:space="preserve">KLEE: Execute: test-rtos/freertos-10.5.1/Source/tasks.c:2201
 </t>
         </is>
       </c>
     </row>
-    <row r="95">
-      <c r="A95" t="inlineStr">
-        <is>
-          <t>test_MPU_pcQueueGetName</t>
-        </is>
-      </c>
-      <c r="B95" t="n">
-        <v>2</v>
-      </c>
-      <c r="C95" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="D95" t="inlineStr">
-        <is>
-          <t>1043</t>
-        </is>
-      </c>
-      <c r="E95" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="F95" t="inlineStr">
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>test_MPU_ulTaskGenericNotifyTake</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr"/>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t xml:space="preserve">KLEE: Execute: test-rtos/freertos-10.5.1/Source/tasks.c:4735
+</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>test_MPU_vTaskSetApplicationTaskTag</t>
+        </is>
+      </c>
+      <c r="B98" t="n">
+        <v>1</v>
+      </c>
+      <c r="C98" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="G95" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="H95" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" t="inlineStr">
-        <is>
-          <t>test_MPU_xQueueSemaphoreTake</t>
-        </is>
-      </c>
-      <c r="B96" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="C96" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="D96" t="inlineStr"/>
-      <c r="E96" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="F96" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="G96" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="H96" t="inlineStr">
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>770</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>test_MPU_xQueueCreateCountingSemaphore</t>
+        </is>
+      </c>
+      <c r="B99" t="n">
+        <v>1</v>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>2361</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>test_MPU_xQueueGenericCreateStatic</t>
+        </is>
+      </c>
+      <c r="B100" t="n">
+        <v>5</v>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>3639</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>test_MPU_pvTimerGetTimerID</t>
+        </is>
+      </c>
+      <c r="B101" t="n">
+        <v>0</v>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>740</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>test_MPU_xQueueReceive</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr"/>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr">
         <is>
           <t xml:space="preserve">KLEE: Execute: test-rtos/freertos-10.5.1/Source/tasks.c:2201
 </t>
         </is>
       </c>
     </row>
-    <row r="97">
-      <c r="A97" t="inlineStr">
-        <is>
-          <t>test_MPU_ulTaskGenericNotifyTake</t>
-        </is>
-      </c>
-      <c r="B97" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="C97" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="D97" t="inlineStr"/>
-      <c r="E97" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="F97" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="G97" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="H97" t="inlineStr">
-        <is>
-          <t xml:space="preserve">KLEE: Execute: test-rtos/freertos-10.5.1/Source/tasks.c:4735
-</t>
-        </is>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" t="inlineStr">
-        <is>
-          <t>test_MPU_vTaskSetApplicationTaskTag</t>
-        </is>
-      </c>
-      <c r="B98" t="n">
-        <v>0</v>
-      </c>
-      <c r="C98" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="D98" t="inlineStr">
-        <is>
-          <t>770</t>
-        </is>
-      </c>
-      <c r="E98" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="F98" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G98" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="H98" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" t="inlineStr">
-        <is>
-          <t>test_MPU_xQueueCreateCountingSemaphore</t>
-        </is>
-      </c>
-      <c r="B99" t="n">
-        <v>3</v>
-      </c>
-      <c r="C99" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="D99" t="inlineStr">
-        <is>
-          <t>2361</t>
-        </is>
-      </c>
-      <c r="E99" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="F99" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G99" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="H99" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" t="inlineStr">
-        <is>
-          <t>test_MPU_xQueueGenericCreateStatic</t>
-        </is>
-      </c>
-      <c r="B100" t="n">
-        <v>17</v>
-      </c>
-      <c r="C100" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="D100" t="inlineStr">
-        <is>
-          <t>3639</t>
-        </is>
-      </c>
-      <c r="E100" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="F100" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G100" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="H100" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" t="inlineStr">
-        <is>
-          <t>test_MPU_pvTimerGetTimerID</t>
-        </is>
-      </c>
-      <c r="B101" t="n">
-        <v>0</v>
-      </c>
-      <c r="C101" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="D101" t="inlineStr">
-        <is>
-          <t>740</t>
-        </is>
-      </c>
-      <c r="E101" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="F101" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G101" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="H101" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" t="inlineStr">
-        <is>
-          <t>test_MPU_xQueueReceive</t>
-        </is>
-      </c>
-      <c r="B102" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="C102" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="D102" t="inlineStr"/>
-      <c r="E102" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="F102" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="G102" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="H102" t="inlineStr">
-        <is>
-          <t xml:space="preserve">KLEE: Execute: test-rtos/freertos-10.5.1/Source/tasks.c:2203
-</t>
-        </is>
-      </c>
-    </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
@@ -4508,7 +5015,7 @@
         </is>
       </c>
       <c r="B103" t="n">
-        <v>28</v>
+        <v>8</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
@@ -4536,6 +5043,11 @@
         </is>
       </c>
       <c r="H103" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr">
         <is>
           <t>NA</t>
         </is>
@@ -4548,7 +5060,7 @@
         </is>
       </c>
       <c r="B104" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
@@ -4562,20 +5074,25 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>34</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>8</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr">
         <is>
           <t>NA</t>
         </is>
@@ -4588,34 +5105,39 @@
         </is>
       </c>
       <c r="B105" t="n">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>405</t>
+          <t>490</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>27881</t>
+          <t>33237</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>268</t>
+          <t>490</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>137</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>38</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr">
         <is>
           <t>NA</t>
         </is>
@@ -4657,6 +5179,11 @@
       </c>
       <c r="H106" t="inlineStr">
         <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr">
+        <is>
           <t>NA</t>
         </is>
       </c>
@@ -4668,7 +5195,7 @@
         </is>
       </c>
       <c r="B107" t="n">
-        <v>0.9142857142857143</v>
+        <v>0.8857142857142857</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
@@ -4692,6 +5219,11 @@
         </is>
       </c>
       <c r="H107" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr">
         <is>
           <t>NA</t>
         </is>

--- a/rtos-api-analysis/results/freertos-10.5.1_runtime_info.xlsx
+++ b/rtos-api-analysis/results/freertos-10.5.1_runtime_info.xlsx
@@ -482,7 +482,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>6</v>
+        <v>44</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -527,7 +527,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -572,7 +572,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -617,7 +617,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -662,7 +662,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -706,30 +706,32 @@
           <t>test_MPU_xQueuePeek</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
+      <c r="B7" t="n">
+        <v>36002</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr"/>
+          <t>32529</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>2029361</t>
+        </is>
+      </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>32507</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>22</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>47</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -739,8 +741,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t xml:space="preserve">KLEE: Execute: test-rtos/freertos-10.5.1/Source/tasks.c:2203
-</t>
+          <t>NA</t>
         </is>
       </c>
     </row>
@@ -751,7 +752,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -796,7 +797,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -841,7 +842,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>6</v>
+        <v>49</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -886,7 +887,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>84</v>
+        <v>555</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -931,7 +932,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1020,30 +1021,32 @@
           <t>test_MPU_xTaskIncrementTick</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
+      <c r="B14" t="n">
+        <v>36006</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr"/>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>219453</t>
+        </is>
+      </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>19</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>8</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1053,8 +1056,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t xml:space="preserve">KLEE: Execute: test-rtos/freertos-10.5.1/Source/tasks.c:2797
-</t>
+          <t>NA</t>
         </is>
       </c>
     </row>
@@ -1065,7 +1067,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>6</v>
+        <v>32</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -1110,7 +1112,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -1155,7 +1157,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -1200,7 +1202,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -1245,7 +1247,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -1290,7 +1292,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -1335,7 +1337,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -1379,30 +1381,32 @@
           <t>test_MPU_xStreamBufferReceive</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
+      <c r="B22" t="n">
+        <v>11316</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
+          <t>12586</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>1027321</t>
+        </is>
+      </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>12586</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>35</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -1412,8 +1416,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t xml:space="preserve">KLEE: Execute: test-rtos/freertos-10.5.1/Source/stream_buffer.c:1329
-</t>
+          <t>NA</t>
         </is>
       </c>
     </row>
@@ -1424,7 +1427,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -1469,7 +1472,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -1559,7 +1562,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -1604,7 +1607,7 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -1649,7 +1652,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -1694,7 +1697,7 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>3</v>
+        <v>22</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -1739,7 +1742,7 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -1784,7 +1787,7 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>3</v>
+        <v>61</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -1829,7 +1832,7 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -1874,7 +1877,7 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -1919,7 +1922,7 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -1964,7 +1967,7 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -2009,7 +2012,7 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -2054,7 +2057,7 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -2099,7 +2102,7 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -2144,7 +2147,7 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -2189,7 +2192,7 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -2233,30 +2236,32 @@
           <t>test_MPU_xQueueSelectFromSet</t>
         </is>
       </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
+      <c r="B41" t="n">
+        <v>29200</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr"/>
+          <t>46999</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>3018607</t>
+        </is>
+      </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>46999</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>46</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -2266,8 +2271,7 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t xml:space="preserve">KLEE: Execute: test-rtos/freertos-10.5.1/Source/tasks.c:3189
-</t>
+          <t>NA</t>
         </is>
       </c>
     </row>
@@ -2278,7 +2282,7 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -2323,7 +2327,7 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -2368,7 +2372,7 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -2413,7 +2417,7 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>3</v>
+        <v>27</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -2458,7 +2462,7 @@
         </is>
       </c>
       <c r="B46" t="n">
-        <v>6619</v>
+        <v>14215</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -2503,7 +2507,7 @@
         </is>
       </c>
       <c r="B47" t="n">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -2548,7 +2552,7 @@
         </is>
       </c>
       <c r="B48" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -2593,7 +2597,7 @@
         </is>
       </c>
       <c r="B49" t="n">
-        <v>12</v>
+        <v>159</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -2638,7 +2642,7 @@
         </is>
       </c>
       <c r="B50" t="n">
-        <v>43</v>
+        <v>334</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -2683,7 +2687,7 @@
         </is>
       </c>
       <c r="B51" t="n">
-        <v>6</v>
+        <v>51</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -2728,7 +2732,7 @@
         </is>
       </c>
       <c r="B52" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -2805,8 +2809,7 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t xml:space="preserve">KLEE: Execute: test-rtos/freertos-10.5.1/Source/tasks.c:4824
-</t>
+          <t>KLEE: Execute: test-rtos/freertos-10.5.1/Source/tasks.c:4824</t>
         </is>
       </c>
     </row>
@@ -2816,30 +2819,32 @@
           <t>test_MPU_xQueueTakeMutexRecursive</t>
         </is>
       </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
+      <c r="B54" t="n">
+        <v>36002</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="D54" t="inlineStr"/>
+          <t>24612</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>1890432</t>
+        </is>
+      </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>24589</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>23</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>49</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -2849,8 +2854,7 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t xml:space="preserve">KLEE: Execute: test-rtos/freertos-10.5.1/Source/tasks.c:2203
-</t>
+          <t>NA</t>
         </is>
       </c>
     </row>
@@ -2861,7 +2865,7 @@
         </is>
       </c>
       <c r="B55" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -2906,7 +2910,7 @@
         </is>
       </c>
       <c r="B56" t="n">
-        <v>5</v>
+        <v>32</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -2951,26 +2955,26 @@
         </is>
       </c>
       <c r="B57" t="n">
-        <v>4317</v>
+        <v>36002</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>90832</t>
+          <t>35609</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>4381845</t>
+          <t>1707928</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>90832</t>
+          <t>35600</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>9</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
@@ -2996,7 +3000,7 @@
         </is>
       </c>
       <c r="B58" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -3041,7 +3045,7 @@
         </is>
       </c>
       <c r="B59" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -3086,7 +3090,7 @@
         </is>
       </c>
       <c r="B60" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -3131,7 +3135,7 @@
         </is>
       </c>
       <c r="B61" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -3176,7 +3180,7 @@
         </is>
       </c>
       <c r="B62" t="n">
-        <v>3</v>
+        <v>22</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -3221,7 +3225,7 @@
         </is>
       </c>
       <c r="B63" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -3266,7 +3270,7 @@
         </is>
       </c>
       <c r="B64" t="n">
-        <v>21</v>
+        <v>133</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -3356,7 +3360,7 @@
         </is>
       </c>
       <c r="B66" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -3401,7 +3405,7 @@
         </is>
       </c>
       <c r="B67" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -3445,30 +3449,32 @@
           <t>test_MPU_xTimerPendFunctionCall</t>
         </is>
       </c>
-      <c r="B68" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
+      <c r="B68" t="n">
+        <v>36002</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="D68" t="inlineStr"/>
+          <t>35170</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>2203094</t>
+        </is>
+      </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>35155</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>15</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>49</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -3478,8 +3484,7 @@
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t xml:space="preserve">KLEE: Execute: test-rtos/freertos-10.5.1/Source/tasks.c:2203
-</t>
+          <t>NA</t>
         </is>
       </c>
     </row>
@@ -3490,7 +3495,7 @@
         </is>
       </c>
       <c r="B69" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -3535,7 +3540,7 @@
         </is>
       </c>
       <c r="B70" t="n">
-        <v>9</v>
+        <v>172</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -3580,7 +3585,7 @@
         </is>
       </c>
       <c r="B71" t="n">
-        <v>228</v>
+        <v>3224</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -3625,7 +3630,7 @@
         </is>
       </c>
       <c r="B72" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -3670,7 +3675,7 @@
         </is>
       </c>
       <c r="B73" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -3715,7 +3720,7 @@
         </is>
       </c>
       <c r="B74" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -3760,7 +3765,7 @@
         </is>
       </c>
       <c r="B75" t="n">
-        <v>149</v>
+        <v>1764</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -3805,7 +3810,7 @@
         </is>
       </c>
       <c r="B76" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -3850,7 +3855,7 @@
         </is>
       </c>
       <c r="B77" t="n">
-        <v>1</v>
+        <v>37</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -3895,7 +3900,7 @@
         </is>
       </c>
       <c r="B78" t="n">
-        <v>291</v>
+        <v>4628</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -3940,7 +3945,7 @@
         </is>
       </c>
       <c r="B79" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -3985,7 +3990,7 @@
         </is>
       </c>
       <c r="B80" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -4030,7 +4035,7 @@
         </is>
       </c>
       <c r="B81" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -4075,7 +4080,7 @@
         </is>
       </c>
       <c r="B82" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -4120,7 +4125,7 @@
         </is>
       </c>
       <c r="B83" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -4129,7 +4134,7 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>9706</t>
+          <t>9704</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
@@ -4144,7 +4149,7 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
@@ -4165,7 +4170,7 @@
         </is>
       </c>
       <c r="B84" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -4210,7 +4215,7 @@
         </is>
       </c>
       <c r="B85" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -4255,7 +4260,7 @@
         </is>
       </c>
       <c r="B86" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -4300,7 +4305,7 @@
         </is>
       </c>
       <c r="B87" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -4345,7 +4350,7 @@
         </is>
       </c>
       <c r="B88" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -4390,7 +4395,7 @@
         </is>
       </c>
       <c r="B89" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -4435,7 +4440,7 @@
         </is>
       </c>
       <c r="B90" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -4480,7 +4485,7 @@
         </is>
       </c>
       <c r="B91" t="n">
-        <v>749</v>
+        <v>8263</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -4524,30 +4529,32 @@
           <t>test_MPU_xTaskCatchUpTicks</t>
         </is>
       </c>
-      <c r="B92" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
+      <c r="B92" t="n">
+        <v>36010</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="D92" t="inlineStr"/>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>212339</t>
+        </is>
+      </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>14</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>31</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>13</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
@@ -4557,8 +4564,7 @@
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t xml:space="preserve">KLEE: Execute: test-rtos/freertos-10.5.1/Source/tasks.c:2793
-</t>
+          <t>NA</t>
         </is>
       </c>
     </row>
@@ -4569,7 +4575,7 @@
         </is>
       </c>
       <c r="B93" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -4613,30 +4619,32 @@
           <t>test_MPU_xQueueGenericSend</t>
         </is>
       </c>
-      <c r="B94" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
+      <c r="B94" t="n">
+        <v>36003</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="D94" t="inlineStr"/>
+          <t>33393</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>1994314</t>
+        </is>
+      </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>33371</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>22</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>52</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
@@ -4646,8 +4654,7 @@
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t xml:space="preserve">KLEE: Execute: test-rtos/freertos-10.5.1/Source/tasks.c:2201
-</t>
+          <t>NA</t>
         </is>
       </c>
     </row>
@@ -4658,7 +4665,7 @@
         </is>
       </c>
       <c r="B95" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -4702,30 +4709,32 @@
           <t>test_MPU_xQueueSemaphoreTake</t>
         </is>
       </c>
-      <c r="B96" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
+      <c r="B96" t="n">
+        <v>36001</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="D96" t="inlineStr"/>
+          <t>32394</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>2021298</t>
+        </is>
+      </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>32370</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>24</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>48</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
@@ -4735,8 +4744,7 @@
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t xml:space="preserve">KLEE: Execute: test-rtos/freertos-10.5.1/Source/tasks.c:2201
-</t>
+          <t>NA</t>
         </is>
       </c>
     </row>
@@ -4779,8 +4787,7 @@
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t xml:space="preserve">KLEE: Execute: test-rtos/freertos-10.5.1/Source/tasks.c:4735
-</t>
+          <t>KLEE: Execute: test-rtos/freertos-10.5.1/Source/tasks.c:4735</t>
         </is>
       </c>
     </row>
@@ -4791,7 +4798,7 @@
         </is>
       </c>
       <c r="B98" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
@@ -4836,7 +4843,7 @@
         </is>
       </c>
       <c r="B99" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
@@ -4881,7 +4888,7 @@
         </is>
       </c>
       <c r="B100" t="n">
-        <v>5</v>
+        <v>65</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
@@ -4926,7 +4933,7 @@
         </is>
       </c>
       <c r="B101" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
@@ -4970,30 +4977,32 @@
           <t>test_MPU_xQueueReceive</t>
         </is>
       </c>
-      <c r="B102" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
+      <c r="B102" t="n">
+        <v>36000</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="D102" t="inlineStr"/>
+          <t>40664</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>2544344</t>
+        </is>
+      </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>40644</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>20</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>47</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
@@ -5003,8 +5012,7 @@
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t xml:space="preserve">KLEE: Execute: test-rtos/freertos-10.5.1/Source/tasks.c:2201
-</t>
+          <t>NA</t>
         </is>
       </c>
     </row>
@@ -5015,7 +5023,7 @@
         </is>
       </c>
       <c r="B103" t="n">
-        <v>8</v>
+        <v>37</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
@@ -5060,7 +5068,7 @@
         </is>
       </c>
       <c r="B104" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
@@ -5105,7 +5113,7 @@
         </is>
       </c>
       <c r="B105" t="n">
-        <v>10</v>
+        <v>108</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
@@ -5150,7 +5158,7 @@
         </is>
       </c>
       <c r="B106" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
@@ -5195,7 +5203,7 @@
         </is>
       </c>
       <c r="B107" t="n">
-        <v>0.8857142857142857</v>
+        <v>0.9809523809523809</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
